--- a/output/pdf_financials_xlsx/EQX.xlsx
+++ b/output/pdf_financials_xlsx/EQX.xlsx
@@ -1325,7 +1325,7 @@
         <v>0.08500000000000001</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-5.422</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0.308</v>
@@ -1553,10 +1553,10 @@
         <v>-0.003847</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5.321</v>
+        <v>-5.321</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.711</v>
+        <v>-2.711</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-18.043</v>
@@ -1724,10 +1724,10 @@
         <v>-0.003847</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5.321</v>
+        <v>-5.321</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.711</v>
+        <v>-2.711</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-18.043</v>
@@ -1901,10 +1901,10 @@
         <v>0.07693999999999999</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>11.085417</v>
+        <v>-11.085417</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>30.122222</v>
+        <v>-30.122222</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>164.027273</v>
@@ -2203,7 +2203,7 @@
         <v>1.623376623376623</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-1.736678883563575</v>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="I32" s="3" t="n">
-        <v>305.6369785794814</v>
+        <v>-305.6369785794814</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-116.6472717869149</v>
@@ -5631,40 +5631,40 @@
         <v>0.235362</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.6185</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>5.504</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.234</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>12.742</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>15.402</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>27.959</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>47.038</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>41.62</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>79.077</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>93.081</v>
       </c>
     </row>
     <row r="93">
@@ -7019,10 +7019,10 @@
         <v>0.015</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.0445</v>
+        <v>-0.259</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.000139</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -10984,7 +10984,11 @@
           <t>Reserves 21</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12460,7 +12464,11 @@
           <t>Reserves 20</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -13692,7 +13700,11 @@
           <t>Reserves 19</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -18330,7 +18342,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -22658,7 +22674,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -24204,7 +24224,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
           <t>-</t>
@@ -26988,7 +27012,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -27738,7 +27766,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -47488,7 +47520,11 @@
           <t>Exploration and evaluation asset expenditure</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -50458,7 +50494,11 @@
           <t>Exploration and evaluation asset expenditure 8</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -52450,7 +52490,11 @@
           <t>Exploration and evaluation asset expenditure 8 (ii)</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -65873,10 +65917,10 @@
         </is>
       </c>
       <c r="L610" s="5" t="n">
-        <v>2.711</v>
+        <v>-2.711</v>
       </c>
       <c r="M610" s="5" t="n">
-        <v>17.429</v>
+        <v>-17.429</v>
       </c>
       <c r="N610" t="inlineStr">
         <is>
@@ -68552,10 +68596,10 @@
         </is>
       </c>
       <c r="K638" s="5" t="n">
-        <v>5.321</v>
+        <v>-5.321</v>
       </c>
       <c r="L638" s="5" t="n">
-        <v>2.711</v>
+        <v>-2.711</v>
       </c>
       <c r="M638" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EQX.xlsx
+++ b/output/pdf_financials_xlsx/EQX.xlsx
@@ -905,13 +905,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.030484</v>
+        <v>0.06873700000000001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.039188</v>
+        <v>0.317958</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.034674</v>
+        <v>0.085466</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.5627</v>
@@ -962,13 +962,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.030484</v>
+        <v>-0.06873700000000001</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.039188</v>
+        <v>-0.317958</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.034674</v>
+        <v>-0.085466</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.5627</v>
@@ -1019,16 +1019,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.003823</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002324</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000616</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>5.2e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0.0094</v>
@@ -1940,16 +1940,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.064914</v>
+        <v>-0.06873700000000001</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.266137</v>
+        <v>-0.268461</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.09285599999999999</v>
+        <v>-0.093472</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.5654</v>
+        <v>-0.565452</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-5.4173</v>
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.064914</v>
+        <v>-0.06873700000000001</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.266137</v>
+        <v>-0.268461</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.09285599999999999</v>
+        <v>-0.093472</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.5631</v>
+        <v>-0.563152</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-5.4153</v>
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.140625</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.268054</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.190142</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.2596000000000001</v>
@@ -2427,13 +2427,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.140625</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.268054</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.190142</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.2596000000000001</v>
@@ -27114,7 +27114,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
@@ -57354,11 +57354,7 @@
           <t>General and administration expense 24</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
           <t>-</t>
@@ -59074,11 +59070,7 @@
           <t>General and administration expense 23</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
           <t>-</t>
@@ -76094,7 +76086,7 @@
       </c>
       <c r="D717" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E717" t="inlineStr">
@@ -76108,10 +76100,10 @@
         </is>
       </c>
       <c r="G717" s="5" t="n">
-        <v>-0.085466</v>
+        <v>0.085466</v>
       </c>
       <c r="H717" s="5" t="n">
-        <v>-0.224994</v>
+        <v>0.224994</v>
       </c>
       <c r="I717" t="inlineStr">
         <is>
@@ -76192,7 +76184,7 @@
       </c>
       <c r="D718" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E718" t="inlineStr">
@@ -76770,7 +76762,7 @@
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E724" t="inlineStr">
@@ -76779,10 +76771,10 @@
         </is>
       </c>
       <c r="F724" s="5" t="n">
-        <v>-0.317958</v>
+        <v>0.317958</v>
       </c>
       <c r="G724" s="5" t="n">
-        <v>-0.085466</v>
+        <v>0.085466</v>
       </c>
       <c r="H724" t="inlineStr">
         <is>
@@ -77836,14 +77828,14 @@
       </c>
       <c r="D735" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E735" s="5" t="n">
-        <v>-0.06873700000000001</v>
+        <v>0.06873700000000001</v>
       </c>
       <c r="F735" s="5" t="n">
-        <v>-0.318461</v>
+        <v>0.318461</v>
       </c>
       <c r="G735" t="inlineStr">
         <is>
@@ -77934,7 +77926,7 @@
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E736" s="5" t="n">
